--- a/#technology_anonymized.xlsx
+++ b/#technology_anonymized.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>关注的userName</t>
+          <t>followed_userName</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>粉丝的userName</t>
+          <t>follower_userName</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>发文量</t>
+          <t>Number of Publications</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -483,12 +483,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -530,12 +530,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -579,12 +579,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -627,12 +627,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -676,12 +676,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -724,12 +724,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -772,12 +772,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -816,12 +816,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -866,12 +866,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -913,12 +913,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -960,12 +960,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -1004,12 +1004,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -1099,12 +1099,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -1147,12 +1147,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1195,12 +1195,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1241,12 +1241,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1288,12 +1288,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1335,12 +1335,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1378,12 +1378,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1425,12 +1425,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1497,12 +1497,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1570,12 +1570,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1607,12 +1607,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1642,12 +1642,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1715,12 +1715,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1751,12 +1751,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1786,12 +1786,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1825,12 +1825,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1861,12 +1861,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1898,12 +1898,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1935,12 +1935,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1973,12 +1973,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2012,12 +2012,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2050,12 +2050,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2088,12 +2088,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2125,12 +2125,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>user_02114</t>
+          <t>user_02138</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2163,12 +2163,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2179,7 +2179,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2214,12 +2214,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2266,12 +2266,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2360,12 +2360,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2410,12 +2410,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2465,12 +2465,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2531,12 +2531,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2588,12 +2588,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2657,12 +2657,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2700,12 +2700,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2751,12 +2751,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2798,12 +2798,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2864,12 +2864,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2926,12 +2926,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2987,12 +2987,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3053,12 +3053,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3109,12 +3109,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3156,12 +3156,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3196,12 +3196,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>user_01571</t>
+          <t>user_01592</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>user_02627</t>
+          <t>user_02683</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3326,12 +3326,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3342,7 +3342,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -3379,12 +3379,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3413,12 +3413,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3447,12 +3447,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3512,12 +3512,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3545,12 +3545,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3578,12 +3578,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3612,12 +3612,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3647,12 +3647,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3681,12 +3681,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3714,12 +3714,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3749,12 +3749,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3783,12 +3783,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3817,12 +3817,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3851,12 +3851,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3885,12 +3885,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3919,12 +3919,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3952,12 +3952,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3987,12 +3987,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4020,12 +4020,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>user_00746</t>
+          <t>user_00759</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>user_00739</t>
+          <t>user_00752</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4052,12 +4052,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>user_00194</t>
+          <t>user_00198</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>user_02237</t>
+          <t>user_02263</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4068,7 +4068,7 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -4090,12 +4090,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>user_00861</t>
+          <t>user_00874</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>user_00862</t>
+          <t>user_00875</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4106,7 +4106,7 @@
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -4128,12 +4128,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>user_01875</t>
+          <t>user_01896</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>user_02162</t>
+          <t>user_02187</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4144,7 +4144,7 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -4169,12 +4169,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>user_01875</t>
+          <t>user_01896</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>user_02162</t>
+          <t>user_02187</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4204,12 +4204,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>user_01875</t>
+          <t>user_01896</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>user_02162</t>
+          <t>user_02187</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4238,12 +4238,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>user_01875</t>
+          <t>user_01896</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>user_02162</t>
+          <t>user_02187</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4272,12 +4272,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>user_01875</t>
+          <t>user_01896</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>user_02162</t>
+          <t>user_02187</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4306,12 +4306,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>user_01875</t>
+          <t>user_01896</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>user_02162</t>
+          <t>user_02187</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4340,12 +4340,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>user_01875</t>
+          <t>user_01896</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>user_02162</t>
+          <t>user_02187</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4374,12 +4374,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>user_01875</t>
+          <t>user_01896</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>user_02162</t>
+          <t>user_02187</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4407,12 +4407,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>user_01875</t>
+          <t>user_01896</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>user_02162</t>
+          <t>user_02187</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4442,12 +4442,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>user_01875</t>
+          <t>user_01896</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>user_02162</t>
+          <t>user_02187</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4478,12 +4478,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>user_01875</t>
+          <t>user_01896</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>user_02162</t>
+          <t>user_02187</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4514,12 +4514,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>user_01530</t>
+          <t>user_01551</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>user_01531</t>
+          <t>user_01552</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4530,7 +4530,7 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -4554,12 +4554,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>user_00620</t>
+          <t>user_00629</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>user_00621</t>
+          <t>user_00630</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4570,7 +4570,7 @@
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -4595,12 +4595,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4611,7 +4611,7 @@
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -4635,12 +4635,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4667,12 +4667,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4700,12 +4700,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4732,12 +4732,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4764,12 +4764,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4797,12 +4797,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4829,12 +4829,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4861,12 +4861,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4893,12 +4893,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4926,12 +4926,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4962,12 +4962,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4995,12 +4995,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5029,12 +5029,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5063,12 +5063,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5104,12 +5104,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5138,12 +5138,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5170,12 +5170,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5203,12 +5203,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5235,12 +5235,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5270,12 +5270,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>user_00542</t>
+          <t>user_00550</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>user_02326</t>
+          <t>user_02361</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5302,12 +5302,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5318,7 +5318,7 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -5341,12 +5341,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5374,12 +5374,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5407,12 +5407,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5440,12 +5440,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5472,12 +5472,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5504,12 +5504,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5536,12 +5536,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5568,12 +5568,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5600,12 +5600,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5632,12 +5632,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5664,12 +5664,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5696,12 +5696,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5728,12 +5728,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5761,12 +5761,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5793,12 +5793,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5825,12 +5825,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5859,12 +5859,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5891,12 +5891,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5923,12 +5923,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5955,12 +5955,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5971,7 +5971,7 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>user_02115</t>
+          <t>user_02139</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -6020,12 +6020,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6053,12 +6053,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6086,12 +6086,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6119,12 +6119,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6154,12 +6154,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6187,12 +6187,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6221,12 +6221,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6255,12 +6255,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6288,12 +6288,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -6320,12 +6320,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -6352,12 +6352,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -6388,12 +6388,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6422,12 +6422,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6456,12 +6456,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -6489,12 +6489,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6522,12 +6522,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6555,12 +6555,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6588,12 +6588,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6622,12 +6622,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>user_00534</t>
+          <t>user_00542</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>user_00483</t>
+          <t>user_00491</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6655,12 +6655,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -6697,12 +6697,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -6740,12 +6740,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -6783,12 +6783,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -6826,12 +6826,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -6868,12 +6868,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -6912,12 +6912,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -6955,12 +6955,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -6998,12 +6998,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -7041,12 +7041,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -7085,12 +7085,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -7128,12 +7128,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -7161,12 +7161,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -7194,12 +7194,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -7227,12 +7227,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -7259,12 +7259,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -7291,12 +7291,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -7323,12 +7323,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -7355,12 +7355,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -7387,12 +7387,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -7419,12 +7419,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7451,12 +7451,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -7483,12 +7483,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -7515,12 +7515,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7548,12 +7548,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7580,12 +7580,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7612,12 +7612,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -7646,12 +7646,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -7678,12 +7678,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -7710,12 +7710,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7742,12 +7742,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7758,7 +7758,7 @@
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -7783,12 +7783,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7799,7 +7799,7 @@
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -7821,12 +7821,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7853,12 +7853,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7886,12 +7886,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7919,12 +7919,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7952,12 +7952,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7985,12 +7985,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -8018,12 +8018,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -8051,12 +8051,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -8083,12 +8083,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -8116,12 +8116,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -8149,12 +8149,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -8181,12 +8181,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -8214,12 +8214,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -8247,12 +8247,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -8283,12 +8283,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -8316,12 +8316,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -8349,12 +8349,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -8381,12 +8381,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -8414,12 +8414,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -8447,12 +8447,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>user_02197</t>
+          <t>user_02222</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>user_02196</t>
+          <t>user_02221</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -8479,12 +8479,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -8495,7 +8495,7 @@
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="F212" t="n">
@@ -8518,12 +8518,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -8551,12 +8551,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -8585,12 +8585,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8617,12 +8617,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -8649,12 +8649,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8681,12 +8681,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8715,12 +8715,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8750,12 +8750,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8782,12 +8782,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8815,12 +8815,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8847,12 +8847,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8879,12 +8879,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8911,12 +8911,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8944,12 +8944,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8976,12 +8976,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -9008,12 +9008,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -9041,12 +9041,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -9073,12 +9073,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -9105,12 +9105,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -9137,12 +9137,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -9171,12 +9171,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -9206,12 +9206,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>user_01774</t>
+          <t>user_01795</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>user_02709</t>
+          <t>user_02769</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -9222,7 +9222,7 @@
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="F234" t="n">
@@ -9244,12 +9244,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>user_01774</t>
+          <t>user_01795</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>user_02709</t>
+          <t>user_02769</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -9286,12 +9286,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>user_01774</t>
+          <t>user_01795</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>user_02709</t>
+          <t>user_02769</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -9318,12 +9318,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>user_01774</t>
+          <t>user_01795</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>user_02709</t>
+          <t>user_02769</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -9350,12 +9350,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>user_01774</t>
+          <t>user_01795</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>user_02709</t>
+          <t>user_02769</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -9384,12 +9384,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>user_01774</t>
+          <t>user_01795</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>user_02709</t>
+          <t>user_02769</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -9417,12 +9417,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>user_01774</t>
+          <t>user_01795</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>user_02709</t>
+          <t>user_02769</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -9453,12 +9453,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>user_02550</t>
+          <t>user_02603</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>user_01291</t>
+          <t>user_01311</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -9469,7 +9469,7 @@
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="F241" t="n">
@@ -9494,12 +9494,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>user_02439</t>
+          <t>user_02483</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>user_02439</t>
+          <t>user_02483</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9510,7 +9510,7 @@
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="F242" t="n">
@@ -9534,12 +9534,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>user_00342</t>
+          <t>user_00350</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>user_02302</t>
+          <t>user_02336</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -9550,7 +9550,7 @@
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="F243" t="n">
@@ -9572,12 +9572,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>user_00364</t>
+          <t>user_00372</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>user_00333</t>
+          <t>user_00341</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9588,7 +9588,7 @@
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="F244" t="n">
@@ -9614,12 +9614,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -9630,7 +9630,7 @@
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="F245" t="n">
@@ -9652,12 +9652,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9685,12 +9685,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9717,12 +9717,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9752,12 +9752,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9784,12 +9784,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9819,12 +9819,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9852,12 +9852,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9887,12 +9887,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9922,12 +9922,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9957,12 +9957,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9990,12 +9990,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -10022,12 +10022,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -10054,12 +10054,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -10086,12 +10086,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -10118,12 +10118,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -10150,12 +10150,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -10183,12 +10183,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -10215,12 +10215,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -10247,12 +10247,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -10280,12 +10280,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>user_00845</t>
+          <t>user_00858</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>user_02398</t>
+          <t>user_02440</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -10313,12 +10313,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -10329,7 +10329,7 @@
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="F266" t="n">
@@ -10353,12 +10353,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -10385,12 +10385,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -10417,12 +10417,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -10449,12 +10449,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -10481,12 +10481,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -10513,12 +10513,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -10545,12 +10545,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -10577,12 +10577,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -10609,12 +10609,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10641,12 +10641,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10673,12 +10673,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -10705,12 +10705,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -10737,12 +10737,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10769,12 +10769,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10801,12 +10801,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10833,12 +10833,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10865,12 +10865,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10897,12 +10897,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -10929,12 +10929,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10961,12 +10961,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>user_00847</t>
+          <t>user_00860</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>user_02400</t>
+          <t>user_02442</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10993,12 +10993,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -11009,7 +11009,7 @@
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
-          <t>user_00862</t>
+          <t>user_00875</t>
         </is>
       </c>
       <c r="F287" t="n">
@@ -11038,12 +11038,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -11054,7 +11054,7 @@
       <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="F288" t="n">
@@ -11077,12 +11077,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -11110,12 +11110,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -11143,12 +11143,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -11176,12 +11176,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -11208,12 +11208,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -11240,12 +11240,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -11272,12 +11272,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -11304,12 +11304,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -11336,12 +11336,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -11368,12 +11368,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -11400,12 +11400,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -11432,12 +11432,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -11464,12 +11464,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -11497,12 +11497,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -11529,12 +11529,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11561,12 +11561,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -11595,12 +11595,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -11627,12 +11627,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -11659,12 +11659,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>user_01365</t>
+          <t>user_01385</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>user_01366</t>
+          <t>user_01386</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -11691,12 +11691,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -11707,7 +11707,7 @@
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="F308" t="n">
@@ -11730,12 +11730,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11763,12 +11763,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -11797,12 +11797,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -11829,12 +11829,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -11861,12 +11861,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -11893,12 +11893,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -11927,12 +11927,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -11962,12 +11962,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -11994,12 +11994,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -12027,12 +12027,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -12059,12 +12059,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -12091,12 +12091,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -12123,12 +12123,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -12156,12 +12156,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -12188,12 +12188,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -12220,12 +12220,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -12253,12 +12253,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -12285,12 +12285,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -12317,12 +12317,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -12349,12 +12349,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -12383,12 +12383,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>user_00484</t>
+          <t>user_00492</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>user_01290</t>
+          <t>user_01310</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -12418,12 +12418,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -12434,7 +12434,7 @@
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -12456,12 +12456,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -12493,12 +12493,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -12526,12 +12526,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -12558,12 +12558,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -12590,12 +12590,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -12623,12 +12623,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -12656,12 +12656,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -12688,12 +12688,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -12720,12 +12720,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -12753,12 +12753,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -12786,12 +12786,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -12818,12 +12818,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -12851,12 +12851,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -12886,12 +12886,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -12918,12 +12918,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -12951,12 +12951,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -12983,12 +12983,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -13016,12 +13016,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -13051,12 +13051,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -13083,12 +13083,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>user_01049</t>
+          <t>user_01064</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>user_01508</t>
+          <t>user_01529</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -13115,12 +13115,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>user_02160</t>
+          <t>user_02185</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>user_02828</t>
+          <t>user_02894</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -13131,7 +13131,7 @@
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="F351" t="n">
@@ -13157,12 +13157,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>user_02160</t>
+          <t>user_02185</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>user_02828</t>
+          <t>user_02894</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -13190,12 +13190,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>user_02160</t>
+          <t>user_02185</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>user_02828</t>
+          <t>user_02894</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -13223,12 +13223,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>user_02160</t>
+          <t>user_02185</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>user_02828</t>
+          <t>user_02894</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -13255,12 +13255,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>user_02160</t>
+          <t>user_02185</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>user_02828</t>
+          <t>user_02894</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -13287,12 +13287,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>user_02160</t>
+          <t>user_02185</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>user_02828</t>
+          <t>user_02894</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -13319,12 +13319,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>user_02160</t>
+          <t>user_02185</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>user_02828</t>
+          <t>user_02894</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -13351,12 +13351,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>user_02160</t>
+          <t>user_02185</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>user_02828</t>
+          <t>user_02894</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -13384,12 +13384,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>user_02160</t>
+          <t>user_02185</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>user_02828</t>
+          <t>user_02894</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -13416,12 +13416,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>user_02160</t>
+          <t>user_02185</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>user_02828</t>
+          <t>user_02894</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -13449,12 +13449,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>user_02160</t>
+          <t>user_02185</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>user_02828</t>
+          <t>user_02894</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -13481,12 +13481,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>user_02160</t>
+          <t>user_02185</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>user_02828</t>
+          <t>user_02894</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -13513,12 +13513,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>user_02160</t>
+          <t>user_02185</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>user_02828</t>
+          <t>user_02894</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -13546,12 +13546,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>user_02160</t>
+          <t>user_02185</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>user_02828</t>
+          <t>user_02894</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -13578,12 +13578,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>user_02160</t>
+          <t>user_02185</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>user_02828</t>
+          <t>user_02894</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -13610,12 +13610,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>user_02033</t>
+          <t>user_02057</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>user_02033</t>
+          <t>user_02057</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -13626,7 +13626,7 @@
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="F366" t="n">
@@ -13648,12 +13648,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -13664,7 +13664,7 @@
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="F367" t="n">
@@ -13686,12 +13686,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -13720,12 +13720,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -13758,12 +13758,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -13790,12 +13790,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -13823,12 +13823,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -13857,12 +13857,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -13891,12 +13891,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -13923,12 +13923,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -13965,12 +13965,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -13999,12 +13999,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -14032,12 +14032,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -14065,12 +14065,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -14097,12 +14097,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -14130,12 +14130,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -14162,12 +14162,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -14194,12 +14194,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -14228,12 +14228,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -14262,12 +14262,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -14296,12 +14296,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -14329,12 +14329,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>user_00197</t>
+          <t>user_00201</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>user_02242</t>
+          <t>user_02268</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -14363,12 +14363,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -14379,7 +14379,7 @@
       <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr">
         <is>
-          <t>user_02404</t>
+          <t>user_02446</t>
         </is>
       </c>
       <c r="F388" t="n">
@@ -14405,12 +14405,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -14437,12 +14437,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -14469,12 +14469,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -14501,12 +14501,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -14534,12 +14534,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -14566,12 +14566,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -14600,12 +14600,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -14632,12 +14632,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -14664,12 +14664,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -14697,12 +14697,12 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -14729,12 +14729,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -14761,12 +14761,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -14793,12 +14793,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -14825,12 +14825,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -14859,12 +14859,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -14891,12 +14891,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -14923,12 +14923,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -14955,12 +14955,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -14987,12 +14987,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -15020,12 +15020,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>user_01226</t>
+          <t>user_01245</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -15052,12 +15052,12 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>user_00861</t>
+          <t>user_00874</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>user_00862</t>
+          <t>user_00875</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -15068,7 +15068,7 @@
       <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -15094,12 +15094,12 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>user_00861</t>
+          <t>user_00874</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>user_00862</t>
+          <t>user_00875</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -15110,7 +15110,7 @@
       <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -15136,12 +15136,12 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>user_00861</t>
+          <t>user_00874</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>user_00862</t>
+          <t>user_00875</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -15152,7 +15152,7 @@
       <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -15180,12 +15180,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>user_00620</t>
+          <t>user_00629</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>user_00621</t>
+          <t>user_00630</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -15196,7 +15196,7 @@
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>user_00862</t>
+          <t>user_00875</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -15221,12 +15221,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -15237,7 +15237,7 @@
       <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr">
         <is>
-          <t>user_00862</t>
+          <t>user_00875</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -15261,12 +15261,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -15293,12 +15293,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -15325,12 +15325,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -15358,12 +15358,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -15390,12 +15390,12 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -15423,12 +15423,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -15458,12 +15458,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -15492,12 +15492,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -15526,12 +15526,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -15558,12 +15558,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -15592,12 +15592,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -15624,12 +15624,12 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -15656,12 +15656,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -15689,12 +15689,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -15722,12 +15722,12 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -15754,12 +15754,12 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>user_01667</t>
+          <t>user_01688</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>user_02674</t>
+          <t>user_02734</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -15787,12 +15787,12 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>user_00737</t>
+          <t>user_00750</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>user_01929</t>
+          <t>user_01951</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -15803,7 +15803,7 @@
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>user_00862</t>
+          <t>user_00875</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -15829,12 +15829,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>user_01779</t>
+          <t>user_01800</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>user_01780</t>
+          <t>user_01801</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -15845,7 +15845,7 @@
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>user_00862</t>
+          <t>user_00875</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -15869,12 +15869,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -15885,7 +15885,7 @@
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>user_00862</t>
+          <t>user_00875</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -15911,12 +15911,12 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -15944,12 +15944,12 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -15977,12 +15977,12 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -16010,12 +16010,12 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -16043,12 +16043,12 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -16076,12 +16076,12 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -16109,12 +16109,12 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -16142,12 +16142,12 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -16175,12 +16175,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -16208,12 +16208,12 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -16240,12 +16240,12 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -16273,12 +16273,12 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -16305,12 +16305,12 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -16338,12 +16338,12 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -16371,12 +16371,12 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -16404,12 +16404,12 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -16440,12 +16440,12 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -16473,12 +16473,12 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -16507,12 +16507,12 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -16540,12 +16540,12 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>user_01393</t>
+          <t>user_01413</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>user_02582</t>
+          <t>user_02635</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -16572,12 +16572,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -16588,7 +16588,7 @@
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>user_00862</t>
+          <t>user_00875</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -16610,12 +16610,12 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -16644,12 +16644,12 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -16677,12 +16677,12 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -16710,12 +16710,12 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -16743,12 +16743,12 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -16777,12 +16777,12 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -16810,12 +16810,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -16843,12 +16843,12 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -16875,12 +16875,12 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -16909,12 +16909,12 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -16942,12 +16942,12 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -16974,12 +16974,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -17007,12 +17007,12 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -17040,12 +17040,12 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -17072,12 +17072,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -17106,12 +17106,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -17139,12 +17139,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -17172,12 +17172,12 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -17206,12 +17206,12 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -17239,12 +17239,12 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>user_01225</t>
+          <t>user_01244</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>user_02544</t>
+          <t>user_02595</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -17271,12 +17271,12 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -17287,7 +17287,7 @@
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>user_00862</t>
+          <t>user_00875</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -17312,12 +17312,12 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -17345,12 +17345,12 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -17378,12 +17378,12 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -17410,12 +17410,12 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -17449,12 +17449,12 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -17481,12 +17481,12 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -17513,12 +17513,12 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -17546,12 +17546,12 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -17578,12 +17578,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -17610,12 +17610,12 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -17643,12 +17643,12 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -17675,12 +17675,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -17707,12 +17707,12 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -17739,12 +17739,12 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -17771,12 +17771,12 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -17803,12 +17803,12 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -17836,12 +17836,12 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -17868,12 +17868,12 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -17900,12 +17900,12 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -17932,12 +17932,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>user_00912</t>
+          <t>user_00925</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>user_00913</t>
+          <t>user_00926</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -17964,12 +17964,12 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -18003,12 +18003,12 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -18042,12 +18042,12 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -18080,12 +18080,12 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -18117,12 +18117,12 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -18150,12 +18150,12 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -18182,12 +18182,12 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -18214,12 +18214,12 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -18248,12 +18248,12 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -18281,12 +18281,12 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -18314,12 +18314,12 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -18346,12 +18346,12 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -18379,12 +18379,12 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -18411,12 +18411,12 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -18443,12 +18443,12 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -18476,12 +18476,12 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -18510,12 +18510,12 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -18543,12 +18543,12 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -18576,12 +18576,12 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -18611,12 +18611,12 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -18644,12 +18644,12 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -18676,12 +18676,12 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -18711,12 +18711,12 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -18746,12 +18746,12 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>user_00355</t>
+          <t>user_00363</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -18780,12 +18780,12 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>user_01738</t>
+          <t>user_01759</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>user_01738</t>
+          <t>user_01759</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -18796,7 +18796,7 @@
       <c r="D519" t="inlineStr"/>
       <c r="E519" t="inlineStr">
         <is>
-          <t>user_00356</t>
+          <t>user_00364</t>
         </is>
       </c>
       <c r="F519" t="n">

--- a/#technology_anonymized.xlsx
+++ b/#technology_anonymized.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6819,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11031,7 +11031,7 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15087,7 +15087,7 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15129,7 +15129,7 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18035,7 +18035,7 @@
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
